--- a/Test upload format/Mudra/IA/2026 - 2027/Update CG Q2.xlsx
+++ b/Test upload format/Mudra/IA/2026 - 2027/Update CG Q2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>custid</t>
   </si>
@@ -86,10 +86,13 @@
     <t>modifiedloancat</t>
   </si>
   <si>
-    <t>Envv16</t>
-  </si>
-  <si>
-    <t>Envv17</t>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>2627CR723</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>Y</t>
@@ -98,22 +101,31 @@
     <t>01-07-2026</t>
   </si>
   <si>
+    <t>40000</t>
+  </si>
+  <si>
     <t>01-04-2026</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Envv18</t>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>2627CR724</t>
+  </si>
+  <si>
+    <t>10000</t>
   </si>
   <si>
     <t>IA</t>
   </si>
   <si>
-    <t>K</t>
+    <t>T</t>
   </si>
 </sst>
 </file>
@@ -287,12 +299,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -626,7 +644,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -650,16 +668,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -668,85 +686,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -764,12 +782,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1119,7 +1135,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1136,9 +1152,12 @@
     <col min="12" max="12" width="14.5714285714286" customWidth="1"/>
     <col min="13" max="13" width="24.8571428571429" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="17.1428571428571" customWidth="1"/>
+    <col min="18" max="18" width="14.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1196,88 +1215,97 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:19">
+    <row r="2" customFormat="1" spans="1:20">
       <c r="A2" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8">
-        <v>1000</v>
+      <c r="C2" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="8">
-        <v>9000</v>
+      <c r="E2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2"/>
+      <c r="K2" s="8">
+        <v>1</v>
+      </c>
+      <c r="L2" s="8">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:20">
+      <c r="A3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2"/>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
+      <c r="G3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="K3" s="8">
         <v>1</v>
       </c>
-      <c r="M2" s="9">
-        <v>100000</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="L3" s="8">
+        <v>1</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" customFormat="1" spans="1:19">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="8">
-        <v>1000</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8">
-        <v>9000</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>1</v>
-      </c>
-      <c r="M3" s="9">
-        <v>100000</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="S3" t="s">
-        <v>28</v>
+      <c r="S3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
